--- a/DTR/2026/MAY16-31/AscendionNew_35311__John_2026-05-16-2026-05-31.xlsx
+++ b/DTR/2026/MAY16-31/AscendionNew_35311__John_2026-05-16-2026-05-31.xlsx
@@ -3304,13 +3304,13 @@
         <v>46160</v>
       </c>
       <c r="F16" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="G16" s="82" t="n">
         <v>0.354166666666667</v>
       </c>
       <c r="H16" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="I16" s="83" t="n">
         <f aca="false">IFERROR(IF(N16="Strict",IF(C16="Normal",IFERROR(IF((HOUR(IF(AQ16&lt;=AR16,BB16-AR16,BB16-AQ16))+MINUTE(IF(AQ16&lt;=AR16,BB16-AR16,BB16-AQ16))/60)&gt;=6,HOUR(IF(AQ16&lt;=AR16,BB16-AR16,BB16-AQ16))+MINUTE(IF(AQ16&lt;=AR16,BB16-AR16,BB16-AQ16))/60-1,HOUR(IF(AQ16&lt;=AR16,BB16-AR16,BB16-AQ16))+MINUTE(IF(AQ16&lt;=AR16,BB16-AR16,BB16-AQ16))/60),0),0),IF(N16="Flexi",IF(C16="Normal",IF((HOUR(BB16-AR16)+MINUTE(BB16-AR16)/60)&gt;=6,(HOUR(BB16-AR16)+MINUTE(BB16-AR16)/60)-1,(HOUR(BB16-AR16)+MINUTE(BB16-AR16)/60)),0),0)),0)</f>
@@ -3474,11 +3474,11 @@
       </c>
       <c r="BB16" s="60" t="str">
         <f aca="false">IF(G16&gt;H16,TEXT(H16,"HH:MM")&amp;" "&amp;TEXT(E16,"DD-mmm-YY"),IF(H16&gt;1,TEXT(H16,"HH:MM")&amp;" "&amp;TEXT(E16,"DD-mmm-YY"),TEXT(H16,"HH:MM")&amp;" "&amp;TEXT(A16,"DD-mmm-YY")))</f>
-        <v>17:30 18-May-26</v>
+        <v>19:30 18-May-26</v>
       </c>
       <c r="BC16" s="60" t="str">
         <f aca="false">IF(N16="Flexi",TEXT(G16+$BC$1,"HH:MM")&amp;" "&amp;TEXT(E16,"DD-mmm-YY"),TEXT(F16,"HH:MM")&amp;" "&amp;TEXT(E16,"DD-mmm-YY"))</f>
-        <v>17:30 18-May-26</v>
+        <v>19:30 18-May-26</v>
       </c>
       <c r="BD16" s="90" t="e">
         <f aca="false" t="array" ref="BD16:BD16">MIN(BB16:BC16+0)</f>
@@ -3770,13 +3770,13 @@
         <v>46161</v>
       </c>
       <c r="F17" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="G17" s="82" t="n">
         <v>0.354166666666667</v>
       </c>
       <c r="H17" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>1.8125</v>
       </c>
       <c r="I17" s="83" t="n">
         <f aca="false">IFERROR(IF(N17="Strict",IF(C17="Normal",IFERROR(IF((HOUR(IF(AQ17&lt;=AR17,BB17-AR17,BB17-AQ17))+MINUTE(IF(AQ17&lt;=AR17,BB17-AR17,BB17-AQ17))/60)&gt;=6,HOUR(IF(AQ17&lt;=AR17,BB17-AR17,BB17-AQ17))+MINUTE(IF(AQ17&lt;=AR17,BB17-AR17,BB17-AQ17))/60-1,HOUR(IF(AQ17&lt;=AR17,BB17-AR17,BB17-AQ17))+MINUTE(IF(AQ17&lt;=AR17,BB17-AR17,BB17-AQ17))/60),0),0),IF(N17="Flexi",IF(C17="Normal",IF((HOUR(BB17-AR17)+MINUTE(BB17-AR17)/60)&gt;=6,(HOUR(BB17-AR17)+MINUTE(BB17-AR17)/60)-1,(HOUR(BB17-AR17)+MINUTE(BB17-AR17)/60)),0),0)),0)</f>
@@ -3940,11 +3940,11 @@
       </c>
       <c r="BB17" s="60" t="str">
         <f aca="false">IF(G17&gt;H17,TEXT(H17,"HH:MM")&amp;" "&amp;TEXT(E17,"DD-mmm-YY"),IF(H17&gt;1,TEXT(H17,"HH:MM")&amp;" "&amp;TEXT(E17,"DD-mmm-YY"),TEXT(H17,"HH:MM")&amp;" "&amp;TEXT(A17,"DD-mmm-YY")))</f>
-        <v>17:30 19-May-26</v>
+        <v>19:30 19-May-26</v>
       </c>
       <c r="BC17" s="60" t="str">
         <f aca="false">IF(N17="Flexi",TEXT(G17+$BC$1,"HH:MM")&amp;" "&amp;TEXT(E17,"DD-mmm-YY"),TEXT(F17,"HH:MM")&amp;" "&amp;TEXT(E17,"DD-mmm-YY"))</f>
-        <v>17:30 19-May-26</v>
+        <v>19:30 19-May-26</v>
       </c>
       <c r="BD17" s="90" t="e">
         <f aca="false" t="array" ref="BD17:BD17">MIN(BB17:BC17+0)</f>
@@ -4236,13 +4236,13 @@
         <v>46162</v>
       </c>
       <c r="F18" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="G18" s="82" t="n">
         <v>0.354166666666667</v>
       </c>
       <c r="H18" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>2.8125</v>
       </c>
       <c r="I18" s="83" t="n">
         <f aca="false">IFERROR(IF(N18="Strict",IF(C18="Normal",IFERROR(IF((HOUR(IF(AQ18&lt;=AR18,BB18-AR18,BB18-AQ18))+MINUTE(IF(AQ18&lt;=AR18,BB18-AR18,BB18-AQ18))/60)&gt;=6,HOUR(IF(AQ18&lt;=AR18,BB18-AR18,BB18-AQ18))+MINUTE(IF(AQ18&lt;=AR18,BB18-AR18,BB18-AQ18))/60-1,HOUR(IF(AQ18&lt;=AR18,BB18-AR18,BB18-AQ18))+MINUTE(IF(AQ18&lt;=AR18,BB18-AR18,BB18-AQ18))/60),0),0),IF(N18="Flexi",IF(C18="Normal",IF((HOUR(BB18-AR18)+MINUTE(BB18-AR18)/60)&gt;=6,(HOUR(BB18-AR18)+MINUTE(BB18-AR18)/60)-1,(HOUR(BB18-AR18)+MINUTE(BB18-AR18)/60)),0),0)),0)</f>
@@ -4406,11 +4406,11 @@
       </c>
       <c r="BB18" s="60" t="str">
         <f aca="false">IF(G18&gt;H18,TEXT(H18,"HH:MM")&amp;" "&amp;TEXT(E18,"DD-mmm-YY"),IF(H18&gt;1,TEXT(H18,"HH:MM")&amp;" "&amp;TEXT(E18,"DD-mmm-YY"),TEXT(H18,"HH:MM")&amp;" "&amp;TEXT(A18,"DD-mmm-YY")))</f>
-        <v>17:30 20-May-26</v>
+        <v>19:30 20-May-26</v>
       </c>
       <c r="BC18" s="60" t="str">
         <f aca="false">IF(N18="Flexi",TEXT(G18+$BC$1,"HH:MM")&amp;" "&amp;TEXT(E18,"DD-mmm-YY"),TEXT(F18,"HH:MM")&amp;" "&amp;TEXT(E18,"DD-mmm-YY"))</f>
-        <v>17:30 20-May-26</v>
+        <v>19:30 20-May-26</v>
       </c>
       <c r="BD18" s="90" t="e">
         <f aca="false" t="array" ref="BD18:BD18">MIN(BB18:BC18+0)</f>
@@ -4702,13 +4702,13 @@
         <v>46163</v>
       </c>
       <c r="F19" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="G19" s="82" t="n">
         <v>0.354166666666667</v>
       </c>
       <c r="H19" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>3.8125</v>
       </c>
       <c r="I19" s="83" t="n">
         <f aca="false">IFERROR(IF(N19="Strict",IF(C19="Normal",IFERROR(IF((HOUR(IF(AQ19&lt;=AR19,BB19-AR19,BB19-AQ19))+MINUTE(IF(AQ19&lt;=AR19,BB19-AR19,BB19-AQ19))/60)&gt;=6,HOUR(IF(AQ19&lt;=AR19,BB19-AR19,BB19-AQ19))+MINUTE(IF(AQ19&lt;=AR19,BB19-AR19,BB19-AQ19))/60-1,HOUR(IF(AQ19&lt;=AR19,BB19-AR19,BB19-AQ19))+MINUTE(IF(AQ19&lt;=AR19,BB19-AR19,BB19-AQ19))/60),0),0),IF(N19="Flexi",IF(C19="Normal",IF((HOUR(BB19-AR19)+MINUTE(BB19-AR19)/60)&gt;=6,(HOUR(BB19-AR19)+MINUTE(BB19-AR19)/60)-1,(HOUR(BB19-AR19)+MINUTE(BB19-AR19)/60)),0),0)),0)</f>
@@ -4872,11 +4872,11 @@
       </c>
       <c r="BB19" s="60" t="str">
         <f aca="false">IF(G19&gt;H19,TEXT(H19,"HH:MM")&amp;" "&amp;TEXT(E19,"DD-mmm-YY"),IF(H19&gt;1,TEXT(H19,"HH:MM")&amp;" "&amp;TEXT(E19,"DD-mmm-YY"),TEXT(H19,"HH:MM")&amp;" "&amp;TEXT(A19,"DD-mmm-YY")))</f>
-        <v>17:30 21-May-26</v>
+        <v>19:30 21-May-26</v>
       </c>
       <c r="BC19" s="60" t="str">
         <f aca="false">IF(N19="Flexi",TEXT(G19+$BC$1,"HH:MM")&amp;" "&amp;TEXT(E19,"DD-mmm-YY"),TEXT(F19,"HH:MM")&amp;" "&amp;TEXT(E19,"DD-mmm-YY"))</f>
-        <v>17:30 21-May-26</v>
+        <v>19:30 21-May-26</v>
       </c>
       <c r="BD19" s="90" t="e">
         <f aca="false" t="array" ref="BD19:BD19">MIN(BB19:BC19+0)</f>
@@ -6524,13 +6524,13 @@
         <v>46167</v>
       </c>
       <c r="F23" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="G23" s="82" t="n">
         <v>0.354166666666667</v>
       </c>
       <c r="H23" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="I23" s="83" t="n">
         <f aca="false">IFERROR(IF(N23="Strict",IF(C23="Normal",IFERROR(IF((HOUR(IF(AQ23&lt;=AR23,BB23-AR23,BB23-AQ23))+MINUTE(IF(AQ23&lt;=AR23,BB23-AR23,BB23-AQ23))/60)&gt;=6,HOUR(IF(AQ23&lt;=AR23,BB23-AR23,BB23-AQ23))+MINUTE(IF(AQ23&lt;=AR23,BB23-AR23,BB23-AQ23))/60-1,HOUR(IF(AQ23&lt;=AR23,BB23-AR23,BB23-AQ23))+MINUTE(IF(AQ23&lt;=AR23,BB23-AR23,BB23-AQ23))/60),0),0),IF(N23="Flexi",IF(C23="Normal",IF((HOUR(BB23-AR23)+MINUTE(BB23-AR23)/60)&gt;=6,(HOUR(BB23-AR23)+MINUTE(BB23-AR23)/60)-1,(HOUR(BB23-AR23)+MINUTE(BB23-AR23)/60)),0),0)),0)</f>
@@ -6694,11 +6694,11 @@
       </c>
       <c r="BB23" s="60" t="str">
         <f aca="false">IF(G23&gt;H23,TEXT(H23,"HH:MM")&amp;" "&amp;TEXT(E23,"DD-mmm-YY"),IF(H23&gt;1,TEXT(H23,"HH:MM")&amp;" "&amp;TEXT(E23,"DD-mmm-YY"),TEXT(H23,"HH:MM")&amp;" "&amp;TEXT(A23,"DD-mmm-YY")))</f>
-        <v>17:30 25-May-26</v>
+        <v>19:30 25-May-26</v>
       </c>
       <c r="BC23" s="60" t="str">
         <f aca="false">IF(N23="Flexi",TEXT(G23+$BC$1,"HH:MM")&amp;" "&amp;TEXT(E23,"DD-mmm-YY"),TEXT(F23,"HH:MM")&amp;" "&amp;TEXT(E23,"DD-mmm-YY"))</f>
-        <v>17:30 25-May-26</v>
+        <v>19:30 25-May-26</v>
       </c>
       <c r="BD23" s="90" t="e">
         <f aca="false" t="array" ref="BD23:BD23">MIN(BB23:BC23+0)</f>
@@ -6990,13 +6990,13 @@
         <v>46168</v>
       </c>
       <c r="F24" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="G24" s="82" t="n">
         <v>0.354166666666667</v>
       </c>
       <c r="H24" s="82" t="n">
-        <v>0.729166666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="I24" s="83" t="n">
         <f aca="false">IFERROR(IF(N24="Strict",IF(C24="Normal",IFERROR(IF((HOUR(IF(AQ24&lt;=AR24,BB24-AR24,BB24-AQ24))+MINUTE(IF(AQ24&lt;=AR24,BB24-AR24,BB24-AQ24))/60)&gt;=6,HOUR(IF(AQ24&lt;=AR24,BB24-AR24,BB24-AQ24))+MINUTE(IF(AQ24&lt;=AR24,BB24-AR24,BB24-AQ24))/60-1,HOUR(IF(AQ24&lt;=AR24,BB24-AR24,BB24-AQ24))+MINUTE(IF(AQ24&lt;=AR24,BB24-AR24,BB24-AQ24))/60),0),0),IF(N24="Flexi",IF(C24="Normal",IF((HOUR(BB24-AR24)+MINUTE(BB24-AR24)/60)&gt;=6,(HOUR(BB24-AR24)+MINUTE(BB24-AR24)/60)-1,(HOUR(BB24-AR24)+MINUTE(BB24-AR24)/60)),0),0)),0)</f>
@@ -7160,11 +7160,11 @@
       </c>
       <c r="BB24" s="60" t="str">
         <f aca="false">IF(G24&gt;H24,TEXT(H24,"HH:MM")&amp;" "&amp;TEXT(E24,"DD-mmm-YY"),IF(H24&gt;1,TEXT(H24,"HH:MM")&amp;" "&amp;TEXT(E24,"DD-mmm-YY"),TEXT(H24,"HH:MM")&amp;" "&amp;TEXT(A24,"DD-mmm-YY")))</f>
-        <v>17:30 26-May-26</v>
+        <v>19:30 26-May-26</v>
       </c>
       <c r="BC24" s="60" t="str">
         <f aca="false">IF(N24="Flexi",TEXT(G24+$BC$1,"HH:MM")&amp;" "&amp;TEXT(E24,"DD-mmm-YY"),TEXT(F24,"HH:MM")&amp;" "&amp;TEXT(E24,"DD-mmm-YY"))</f>
-        <v>17:30 26-May-26</v>
+        <v>19:30 26-May-26</v>
       </c>
       <c r="BD24" s="90" t="e">
         <f aca="false" t="array" ref="BD24:BD24">MIN(BB24:BC24+0)</f>
